--- a/InputData/elec/RPfFESCC/RPfFESCC Repayment Period for Financed Elec Sector Capital Costs.xlsx
+++ b/InputData/elec/RPfFESCC/RPfFESCC Repayment Period for Financed Elec Sector Capital Costs.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\robbie\Dropbox (Energy Innovation)\My Documents\Energy Policy Solutions\US\Models\eps-us\InputData\elec\RPfFESCC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\elec\RPfFESCC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80EC3107-A379-4815-A725-E40D4B74474C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6029335A-F32B-4B15-807C-3ED374EE4723}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
     <sheet name="RPfFESCC" sheetId="17" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -28,8 +28,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -39,10 +37,28 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
+    <t>Source:</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
     <t>RPfFESCC Repayment Period for Financed Electricity Sector Capital Costs</t>
   </si>
   <si>
-    <t>Source:</t>
+    <t>This variable is used with Vensim's DEPRECIATE STRAIGHTLINE function to spread repayment of electricity sector</t>
+  </si>
+  <si>
+    <t>capital costs over a set number of years.</t>
+  </si>
+  <si>
+    <t>repayment period</t>
+  </si>
+  <si>
+    <t>Unit: years</t>
+  </si>
+  <si>
+    <t>Time Period</t>
   </si>
   <si>
     <t>National Renewable Energy Laboratory</t>
@@ -51,35 +67,17 @@
     <t>Annual Technology Baseline</t>
   </si>
   <si>
+    <t>We use 30 years because this is the default period used in NREL's Annual Electricity Technology Baseline.</t>
+  </si>
+  <si>
     <t>https://atb.nrel.gov/electricity/2023/index</t>
-  </si>
-  <si>
-    <t>Notes</t>
-  </si>
-  <si>
-    <t>This variable is used with Vensim's DEPRECIATE STRAIGHTLINE function to spread repayment of electricity sector</t>
-  </si>
-  <si>
-    <t>capital costs over a set number of years.</t>
-  </si>
-  <si>
-    <t>We use 30 years because this is the default period used in NREL's Annual Electricity Technology Baseline.</t>
-  </si>
-  <si>
-    <t>Unit: years</t>
-  </si>
-  <si>
-    <t>Time Period</t>
-  </si>
-  <si>
-    <t>repayment period</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -177,7 +175,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="3" applyFill="1"/>
   </cellXfs>
   <cellStyles count="4">
-    <cellStyle name="Hipervínculo" xfId="3" builtinId="8"/>
+    <cellStyle name="Hyperlink" xfId="3" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
     <cellStyle name="Normal 3" xfId="2" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
@@ -459,125 +457,125 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D29"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="93" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="B3" s="2" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D3" s="4"/>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B4" s="7">
         <v>2023</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B6" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A9" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A10" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="B6" s="8" t="s">
+      <c r="B10" s="2"/>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B10" s="2"/>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" t="s">
-        <v>7</v>
-      </c>
       <c r="B11" s="2"/>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B13" s="2"/>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
     </row>
-    <row r="16" spans="1:4">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
     </row>
-    <row r="18" spans="1:2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B18" s="2"/>
     </row>
-    <row r="19" spans="1:2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
     </row>
-    <row r="20" spans="1:2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
     </row>
-    <row r="21" spans="1:2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
     </row>
-    <row r="22" spans="1:2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
     </row>
-    <row r="23" spans="1:2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B23" s="2"/>
     </row>
-    <row r="24" spans="1:2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
     </row>
-    <row r="25" spans="1:2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
     </row>
-    <row r="26" spans="1:2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
     </row>
-    <row r="27" spans="1:2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B27" s="2"/>
     </row>
-    <row r="28" spans="1:2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
     </row>
-    <row r="29" spans="1:2">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
     </row>
@@ -596,201 +594,30 @@
     <tabColor theme="8" tint="-0.499984740745262"/>
   </sheetPr>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="25.5703125" customWidth="1"/>
+    <col min="1" max="1" width="25.54296875" customWidth="1"/>
     <col min="2" max="2" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="B2" s="3">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009A9DAB439B36DB4795F39C4E722C7BC4" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="44674c89fa9bc5e97a878a6680c46188">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="79748b23-d81a-423e-9112-21109dc864e6" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="447839a363ea5a12024b5bf1ab53ed90" ns2:_="">
-    <xsd:import namespace="79748b23-d81a-423e-9112-21109dc864e6"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="79748b23-d81a-423e-9112-21109dc864e6" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{07CA1D1E-CEFF-4DBA-BBAF-AFA35AB6952B}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{70D3715F-C0FF-43D8-B710-72D636CD14F7}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{479082AB-63A9-4A70-B2FF-94D510120C5A}"/>
 </file>